--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008414815340366153</v>
       </c>
       <c r="C2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>23372335</v>
+        <v>4363364</v>
       </c>
       <c r="L2" t="n">
-        <v>13934302</v>
+        <v>2375307</v>
       </c>
       <c r="M2" t="n">
-        <v>3560170</v>
+        <v>528087</v>
       </c>
       <c r="N2" t="n">
-        <v>214667</v>
+        <v>24194</v>
       </c>
       <c r="O2" t="n">
-        <v>2112141</v>
+        <v>341697</v>
       </c>
       <c r="P2" t="n">
-        <v>842201</v>
+        <v>144106</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999932646751404</v>
+        <v>0.9999865889549255</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9219809174537659</v>
+        <v>0.8524977564811707</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8336419463157654</v>
+        <v>0.7042760848999023</v>
       </c>
       <c r="T2" t="n">
-        <v>0.79982590675354</v>
+        <v>0.6420409083366394</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6074214577674866</v>
+        <v>0.2907967567443848</v>
       </c>
       <c r="V2" t="n">
-        <v>0.836666464805603</v>
+        <v>0.700475811958313</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8830648064613342</v>
+        <v>0.7789766192436218</v>
       </c>
       <c r="X2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565883278846741</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112817645072937</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580537438392639</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622784733772278</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019806981086731</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002016582438865534</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>23372335</v>
+        <v>4363364</v>
       </c>
       <c r="E3" t="n">
-        <v>1915514</v>
+        <v>675560</v>
       </c>
       <c r="F3" t="n">
-        <v>24825</v>
+        <v>10765</v>
       </c>
       <c r="G3" t="n">
-        <v>3594</v>
+        <v>1281</v>
       </c>
       <c r="H3" t="n">
-        <v>1580</v>
+        <v>861</v>
       </c>
       <c r="I3" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="J3" t="n">
-        <v>50347886</v>
+        <v>10069535</v>
       </c>
       <c r="K3" t="n">
-        <v>54784236</v>
+        <v>10609151</v>
       </c>
       <c r="L3" t="n">
-        <v>62899785</v>
+        <v>12128514</v>
       </c>
       <c r="M3" t="n">
-        <v>76518421</v>
+        <v>15186456</v>
       </c>
       <c r="N3" t="n">
-        <v>81494680</v>
+        <v>16267576</v>
       </c>
       <c r="O3" t="n">
-        <v>79120817</v>
+        <v>15760184</v>
       </c>
       <c r="P3" t="n">
-        <v>81001891</v>
+        <v>16181719</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9231520295143127</v>
+        <v>0.8637102246284485</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8496761322021484</v>
+        <v>0.7219558954238892</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7622563242912292</v>
+        <v>0.5647276639938354</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4806910157203674</v>
+        <v>0.2705689072608948</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8293144106864929</v>
+        <v>0.6703805923461914</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8713160157203674</v>
+        <v>0.7451459169387817</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>995349</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>42884</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>34102</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50348100</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55661737</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>64227600</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76746838</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81482703</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79283607</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>81047145</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576305150985718</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099767208099365</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575676679611206</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618276834487915</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016205072402954</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03185715663591164</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1870201</v>
+        <v>715462</v>
       </c>
       <c r="E4" t="n">
-        <v>13934302</v>
+        <v>2375307</v>
       </c>
       <c r="F4" t="n">
-        <v>537532</v>
+        <v>171796</v>
       </c>
       <c r="G4" t="n">
-        <v>17401</v>
+        <v>8545</v>
       </c>
       <c r="H4" t="n">
-        <v>36975</v>
+        <v>17230</v>
       </c>
       <c r="I4" t="n">
-        <v>3132</v>
+        <v>1759</v>
       </c>
       <c r="J4" t="n">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="K4" t="n">
-        <v>1977794</v>
+        <v>754965</v>
       </c>
       <c r="L4" t="n">
-        <v>2780670</v>
+        <v>997386</v>
       </c>
       <c r="M4" t="n">
-        <v>891011</v>
+        <v>294426</v>
       </c>
       <c r="N4" t="n">
-        <v>138740</v>
+        <v>59005</v>
       </c>
       <c r="O4" t="n">
-        <v>412331</v>
+        <v>146110</v>
       </c>
       <c r="P4" t="n">
-        <v>111524</v>
+        <v>40888</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999966025352478</v>
+        <v>0.9999932646751404</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9225661158561707</v>
+        <v>0.8580673336982727</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8415826559066772</v>
+        <v>0.7130064368247986</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7805892825126648</v>
+        <v>0.6009077429771423</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5366761684417725</v>
+        <v>0.2803183794021606</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8329742550849915</v>
+        <v>0.685097873210907</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8771510720252991</v>
+        <v>0.761685848236084</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1027338</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>415378</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27557</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1100293</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1452855</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>662594</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>150717</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249541</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571090936660767</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106287360191345</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578105568885803</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620529890060425</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018005132675171</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>65909</v>
+        <v>25696</v>
       </c>
       <c r="E5" t="n">
-        <v>745834</v>
+        <v>276404</v>
       </c>
       <c r="F5" t="n">
-        <v>3560170</v>
+        <v>528087</v>
       </c>
       <c r="G5" t="n">
-        <v>57963</v>
+        <v>21842</v>
       </c>
       <c r="H5" t="n">
-        <v>224989</v>
+        <v>75384</v>
       </c>
       <c r="I5" t="n">
-        <v>15695</v>
+        <v>7702</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1945635</v>
+        <v>688520</v>
       </c>
       <c r="L5" t="n">
-        <v>2465243</v>
+        <v>914793</v>
       </c>
       <c r="M5" t="n">
-        <v>1110398</v>
+        <v>407031</v>
       </c>
       <c r="N5" t="n">
-        <v>231913</v>
+        <v>65225</v>
       </c>
       <c r="O5" t="n">
-        <v>434711</v>
+        <v>168009</v>
       </c>
       <c r="P5" t="n">
-        <v>124384</v>
+        <v>49287</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999973773956299</v>
+        <v>0.9999948143959045</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9521999359130859</v>
+        <v>0.9120684266090393</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9360877871513367</v>
+        <v>0.8835173845291138</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9756163358688354</v>
+        <v>0.9572699069976807</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9954842329025269</v>
+        <v>0.9924323558807373</v>
       </c>
       <c r="V5" t="n">
-        <v>0.989680290222168</v>
+        <v>0.9808650612831116</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9971258640289307</v>
+        <v>0.9945068955421448</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40265</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>426214</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49808</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145788</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1072710</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1476341</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>665240</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>151021</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250558</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735257625579834</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643129110336304</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838227033615112</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963238835334778</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939071536064148</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383641242981</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>41179</v>
+        <v>13455</v>
       </c>
       <c r="E6" t="n">
-        <v>74514</v>
+        <v>20245</v>
       </c>
       <c r="F6" t="n">
-        <v>74301</v>
+        <v>19770</v>
       </c>
       <c r="G6" t="n">
-        <v>214667</v>
+        <v>24194</v>
       </c>
       <c r="H6" t="n">
-        <v>38110</v>
+        <v>10350</v>
       </c>
       <c r="I6" t="n">
-        <v>3752</v>
+        <v>1382</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32411</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26831</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54451</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34923</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="E7" t="n">
-        <v>42672</v>
+        <v>23967</v>
       </c>
       <c r="F7" t="n">
-        <v>246098</v>
+        <v>87920</v>
       </c>
       <c r="G7" t="n">
-        <v>56703</v>
+        <v>25798</v>
       </c>
       <c r="H7" t="n">
-        <v>2112141</v>
+        <v>341697</v>
       </c>
       <c r="I7" t="n">
-        <v>88832</v>
+        <v>29997</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4056</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148230</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37923</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>2136</v>
+        <v>1210</v>
       </c>
       <c r="F8" t="n">
-        <v>8255</v>
+        <v>4175</v>
       </c>
       <c r="G8" t="n">
-        <v>3079</v>
+        <v>1539</v>
       </c>
       <c r="H8" t="n">
-        <v>110677</v>
+        <v>42285</v>
       </c>
       <c r="I8" t="n">
-        <v>842201</v>
+        <v>144106</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
